--- a/data/trans_camb/P7_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P7_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 15,55</t>
+          <t>1,18; 15,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 14,96</t>
+          <t>0,71; 15,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 14,13</t>
+          <t>0,92; 14,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,8; 29,58</t>
+          <t>13,72; 29,83</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,61; 23,05</t>
+          <t>8,35; 22,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,12; 21,91</t>
+          <t>7,85; 21,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 20,73</t>
+          <t>9,88; 19,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 16,43</t>
+          <t>6,77; 16,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 15,48</t>
+          <t>6,06; 16,04</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 120,43</t>
+          <t>3,33; 114,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 115,23</t>
+          <t>2,28; 116,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 109,41</t>
+          <t>3,43; 111,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,17; 199,42</t>
+          <t>61,66; 206,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,97; 152,48</t>
+          <t>37,2; 155,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,05; 149,21</t>
+          <t>34,12; 149,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,69; 140,18</t>
+          <t>49,09; 132,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>30,86; 109,75</t>
+          <t>32,18; 112,71</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,1; 104,36</t>
+          <t>30,6; 107,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 4,93</t>
+          <t>-4,76; 5,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 1,85</t>
+          <t>-7,72; 1,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 2,37</t>
+          <t>-7,34; 2,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,22</t>
+          <t>-6,59; 4,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,4; -3,8</t>
+          <t>-14,74; -4,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,63; -8,95</t>
+          <t>-18,98; -8,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,28</t>
+          <t>-4,69; 3,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,0; -2,44</t>
+          <t>-10,0; -2,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -4,59</t>
+          <t>-11,89; -4,43</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 31,58</t>
+          <t>-23,85; 35,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,99; 12,41</t>
+          <t>-38,32; 12,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 15,51</t>
+          <t>-38,18; 17,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,61; 17,45</t>
+          <t>-19,42; 16,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,17; -12,94</t>
+          <t>-42,29; -13,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,17; -30,93</t>
+          <t>-52,87; -30,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 14,41</t>
+          <t>-17,51; 14,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,25; -10,75</t>
+          <t>-37,19; -10,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-45,48; -19,93</t>
+          <t>-44,26; -19,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 7,01</t>
+          <t>-4,6; 7,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,66</t>
+          <t>-6,89; 3,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 10,03</t>
+          <t>-0,87; 9,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -1,95</t>
+          <t>-15,86; -1,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,76; -9,6</t>
+          <t>-22,22; -8,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,53; -4,2</t>
+          <t>-16,52; -4,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 0,87</t>
+          <t>-8,42; 0,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,16; -4,44</t>
+          <t>-13,03; -4,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 1,32</t>
+          <t>-7,23; 1,09</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,77; 60,56</t>
+          <t>-27,23; 61,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 33,02</t>
+          <t>-39,05; 31,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 87,13</t>
+          <t>-5,39; 84,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,36; -6,39</t>
+          <t>-43,97; -5,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,54; -32,47</t>
+          <t>-61,69; -30,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,47; -14,9</t>
+          <t>-46,08; -15,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 4,06</t>
+          <t>-32,27; 2,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,43; -19,93</t>
+          <t>-50,34; -22,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-27,67; 6,41</t>
+          <t>-27,89; 5,14</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,97; 13,65</t>
+          <t>2,51; 13,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 12,82</t>
+          <t>1,89; 13,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 15,43</t>
+          <t>2,66; 14,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 13,33</t>
+          <t>-0,24; 13,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,61</t>
+          <t>-3,4; 10,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 1,45</t>
+          <t>-16,28; 1,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,5</t>
+          <t>2,73; 11,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 9,48</t>
+          <t>0,9; 9,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 5,83</t>
+          <t>-5,6; 5,58</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,86; 151,28</t>
+          <t>17,24; 143,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,78; 142,08</t>
+          <t>12,3; 142,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,71; 167,69</t>
+          <t>19,41; 158,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 54,13</t>
+          <t>-0,73; 54,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,97; 40,1</t>
+          <t>-11,06; 41,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-54,42; 5,47</t>
+          <t>-52,63; 4,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,22; 66,61</t>
+          <t>13,65; 64,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,5; 54,49</t>
+          <t>4,19; 55,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 32,21</t>
+          <t>-25,51; 30,36</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 3,36</t>
+          <t>-12,42; 3,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 8,43</t>
+          <t>-7,65; 8,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -3,85</t>
+          <t>-16,77; -4,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 4,38</t>
+          <t>-13,93; 4,55</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-18,17; 1,54</t>
+          <t>-17,6; 0,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,23; -12,73</t>
+          <t>-31,19; -12,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 1,38</t>
+          <t>-10,24; 1,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 2,19</t>
+          <t>-10,07; 1,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-20,92; -10,0</t>
+          <t>-21,44; -9,58</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 21,01</t>
+          <t>-51,36; 20,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-33,89; 50,35</t>
+          <t>-31,5; 50,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-67,68; -24,44</t>
+          <t>-67,38; -25,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,65; 14,94</t>
+          <t>-35,18; 14,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 6,07</t>
+          <t>-43,46; 2,33</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,82; -40,99</t>
+          <t>-77,72; -40,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,34; 5,87</t>
+          <t>-33,18; 4,76</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 9,02</t>
+          <t>-32,2; 5,97</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-68,5; -39,67</t>
+          <t>-68,64; -39,09</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,15; 12,12</t>
+          <t>-0,3; 12,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 10,02</t>
+          <t>-1,72; 10,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,08; 15,91</t>
+          <t>3,88; 15,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 1,39</t>
+          <t>-13,27; 2,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -0,68</t>
+          <t>-16,41; -1,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 1,28</t>
+          <t>-12,37; 1,29</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 4,68</t>
+          <t>-5,26; 4,48</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 2,53</t>
+          <t>-7,78; 2,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 5,69</t>
+          <t>-2,53; 6,01</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0,55; 120,65</t>
+          <t>-2,5; 127,33</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-13,67; 100,3</t>
+          <t>-12,09; 106,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>22,23; 155,29</t>
+          <t>22,61; 160,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 4,95</t>
+          <t>-36,41; 7,61</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-45,79; -0,98</t>
+          <t>-45,37; -3,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-32,97; 4,32</t>
+          <t>-32,68; 4,73</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 22,77</t>
+          <t>-20,36; 21,67</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,57; 11,76</t>
+          <t>-29,88; 13,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 27,57</t>
+          <t>-10,18; 29,64</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 4,79</t>
+          <t>-3,18; 4,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,7</t>
+          <t>-3,68; 4,1</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,96</t>
+          <t>-3,49; 4,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-10,14; -0,13</t>
+          <t>-10,45; -1,01</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 0,33</t>
+          <t>-9,68; 0,25</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-20,51; -2,95</t>
+          <t>-21,8; -3,17</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 0,85</t>
+          <t>-5,32; 1,37</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 1,2</t>
+          <t>-5,6; 0,9</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -0,67</t>
+          <t>-11,52; -0,51</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,82; 39,66</t>
+          <t>-20,82; 38,18</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 39,86</t>
+          <t>-23,39; 34,8</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 43,76</t>
+          <t>-21,9; 37,81</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-32,77; -0,28</t>
+          <t>-33,29; -3,98</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 1,26</t>
+          <t>-31,01; 1,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-67,57; -10,74</t>
+          <t>-71,15; -11,26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 4,31</t>
+          <t>-23,02; 6,84</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-23,24; 6,27</t>
+          <t>-24,29; 5,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-51,05; -3,5</t>
+          <t>-51,48; -2,6</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -1,24</t>
+          <t>-8,8; -1,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-8,91; -1,81</t>
+          <t>-9,1; -1,98</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 1,7</t>
+          <t>-13,13; 1,84</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -2,4</t>
+          <t>-10,85; -2,82</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-9,66; -0,58</t>
+          <t>-9,05; -0,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 4,61</t>
+          <t>-3,56; 4,63</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-8,64; -2,83</t>
+          <t>-8,7; -3,13</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -2,1</t>
+          <t>-8,18; -2,4</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 1,62</t>
+          <t>-10,45; 1,64</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-44,22; -8,01</t>
+          <t>-45,04; -7,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -11,18</t>
+          <t>-45,62; -12,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-69,35; 9,61</t>
+          <t>-66,21; 11,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-39,66; -11,52</t>
+          <t>-39,38; -11,87</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-34,53; -1,99</t>
+          <t>-33,12; -2,48</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 20,06</t>
+          <t>-12,91; 20,96</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-37,13; -13,93</t>
+          <t>-37,13; -15,49</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-33,8; -10,65</t>
+          <t>-35,03; -12,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 7,57</t>
+          <t>-45,85; 7,76</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,9</t>
+          <t>-0,74; 2,88</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,82</t>
+          <t>-1,8; 1,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,91</t>
+          <t>-3,03; 3,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,26</t>
+          <t>-4,18; 0,25</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,81; -2,63</t>
+          <t>-6,76; -2,58</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-10,94; -4,09</t>
+          <t>-10,7; -4,01</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,84</t>
+          <t>-1,84; 1,03</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,87; -1,03</t>
+          <t>-3,66; -0,87</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-5,39; -1,11</t>
+          <t>-5,86; -1,23</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 19,81</t>
+          <t>-4,53; 19,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 12,22</t>
+          <t>-10,81; 12,42</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 19,1</t>
+          <t>-18,01; 19,7</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 1,07</t>
+          <t>-14,19; 1,13</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-23,1; -9,44</t>
+          <t>-22,65; -9,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -14,8</t>
+          <t>-37,15; -14,92</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 3,91</t>
+          <t>-8,01; 4,81</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,73; -4,85</t>
+          <t>-16,11; -4,22</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-23,76; -4,93</t>
+          <t>-25,64; -5,73</t>
         </is>
       </c>
     </row>
